--- a/excel/universities/hanken-school-of-economics.xlsx
+++ b/excel/universities/hanken-school-of-economics.xlsx
@@ -115,7 +115,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.hanken.fi/en/apply</t>
+          <t xml:space="preserve">https://www.hanken.fi/en/apply/application/masters-degree-studies-english</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -125,7 +125,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Master's degree studies in English</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -140,12 +140,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Programme-specific</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fill program-specific information here</t>
+          <t xml:space="preserve">Hanken publishes separate Main Admission and Rolling Admission rounds for English master's programmes.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -161,7 +161,7 @@
 
 <file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -229,7 +229,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Main Admission round</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -239,12 +239,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-01-07</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-01-21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -254,15 +254,67 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.hanken.fi/en/apply</t>
+          <t xml:space="preserve">https://www.hanken.fi/en/apply/application/masters-degree-studies-english/main-admission-round/application-process-step-step</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify annual deadlines</t>
+          <t xml:space="preserve">Attachment deadline 2026-01-28; all results published by 2026-05-27.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling Admission round</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-08</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-15</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/index.php/en/apply/application/masters-degree-studies-english</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling Admission is limited to selected programmes and applicants with bachelor's degrees in economic sciences obtained outside Finland.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
@@ -275,7 +327,7 @@
 
 <file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -333,12 +385,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Main Admission round</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passport</t>
+          <t xml:space="preserve">Degree certificate</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -348,15 +400,225 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Diploma supplement is part of the requested educational documents when available.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.hanken.fi/en/apply</t>
+          <t xml:space="preserve">https://www.hanken.fi/en/apply/application/masters-degree-studies-english/attachments</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Main Admission round</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transcript of records</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official translations are required if documents are not in English Finnish or Swedish.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/apply/application/masters-degree-studies-english/attachments</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Main Admission round</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GPA or GMAT GRE report</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check programme</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken requests GPA or GMAT or GRE documentation depending on programme and track.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/apply/application/masters-degree-studies-english/attachments</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Main Admission round</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Certificate of language proficiency</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Submit as high-quality scanned PDF.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/apply/application/masters-degree-studies-english/attachments</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Main Admission round</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CV in English</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conditional</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Required in main admission and for selected rolling-admission tracks.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/apply/application/masters-degree-studies-english/attachments</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Main Admission round</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Passport or EU identity card</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Residence permit copy is needed where applicable.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/apply/application/masters-degree-studies-english/attachments</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
@@ -369,7 +631,7 @@
 
 <file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -420,15 +682,30 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">citation_source</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citation_last_checked</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t xml:space="preserve">official_profile_url</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">email</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">last_verified</t>
         </is>
@@ -437,7 +714,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hanken School of Economics</t>
+          <t xml:space="preserve">University Name</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,7 +734,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research Area 1; Research Area 2</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -482,7 +759,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.hanken.fi/en</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -492,7 +769,22 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-14</t>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>

--- a/excel/universities/hanken-school-of-economics.xlsx
+++ b/excel/universities/hanken-school-of-economics.xlsx
@@ -631,7 +631,7 @@
 
 <file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -714,17 +714,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">University Name</t>
+          <t xml:space="preserve">Hanken School of Economics</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Department Name</t>
+          <t xml:space="preserve">Department of Management and Organisation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor Name</t>
+          <t xml:space="preserve">Denise Salin</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Management and organisation; Workplace bullying; Leadership; Gender and diversity</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -749,27 +749,27 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">4296</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hanken official profile</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.hanken.fi/en/person/denise-salin</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -784,7 +784,161 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Official Hanken profile states citation and h-index figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Marketing</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kaj Storbacka</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Markets and strategy; Sales management; Business model innovation; Customer relationships</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken official profile</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/person/kaj-storbacka</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken official profile used for title and research focus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Economics</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joacim Tag</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assistant Professor</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Economics; Applied econometrics; Productivity; Labor markets</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">750</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken official profile</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/person/joacim-tag</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official Hanken profile states citation and h-index figures.</t>
         </is>
       </c>
     </row>

--- a/excel/universities/hanken-school-of-economics.xlsx
+++ b/excel/universities/hanken-school-of-economics.xlsx
@@ -20,7 +20,8 @@
     <sheet name="UniversityInfo" sheetId="1" r:id="rId1"/>
     <sheet name="Deadlines" sheetId="2" r:id="rId2"/>
     <sheet name="Documents" sheetId="3" r:id="rId3"/>
-    <sheet name="Professors" sheetId="4" r:id="rId4"/>
+    <sheet name="Departments" sheetId="4" r:id="rId4"/>
+    <sheet name="Professors" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -631,6 +632,251 @@
 
 <file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">university_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unit_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unit_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parent_unit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campus_or_city</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">focus_areas</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">official_url</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">last_verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Accounting and Commercial Law</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accounting; Commercial law</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/departments-and-centres</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official departments and centres page.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Economics</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Economics; Statistics</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/departments-and-centres</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official departments and centres page.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Management and Organisation</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Management; Organisation; Information systems science</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/departments-and-centres</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official departments and centres page.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Marketing</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marketing; Supply chain management; Social responsibility</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/departments-and-centres</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official departments and centres page.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
